--- a/json2tsv/マッピング表.xlsx
+++ b/json2tsv/マッピング表.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <x:workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\library\Downloads\20260203_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E48DED-DBE0-4929-A90F-C83F13D89282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="1820" yWindow="1820" windowWidth="28800" windowHeight="15200" xr2:uid="{FDB381A2-074E-4C1F-B0A7-D26236122CBF}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$42</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <x:bookViews>
+    <x:workbookView xWindow="1820" yWindow="1820" windowWidth="28800" windowHeight="15200" xr2:uid="{FDB381A2-074E-4C1F-B0A7-D26236122CBF}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$42</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029"/>
+  <x:extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    </x:ext>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -31,12 +31,12 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+    </x:ext>
+    <x:ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1936,928 +1936,1510 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4BEA64-0C96-4527-8A58-FFDEC4514951}">
-  <dimension ref="A1:H42"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="66.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.58203125" customWidth="1"/>
-    <col min="3" max="3" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.9140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="5">
-        <v>110</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" ht="270" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="5">
-        <v>1207000000</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G39" s="5">
-        <v>12</v>
-      </c>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G40" s="5">
-        <v>4</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="H42" s="1"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:H42" xr:uid="{5A4BEA64-0C96-4527-8A58-FFDEC4514951}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{5A4BEA64-0C96-4527-8A58-FFDEC4514951}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:dimension ref="A1:H60"/>
+  <x:sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <x:cols>
+    <x:col min="1" max="1" width="66.6640625" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="25.58203125" customWidth="1"/>
+    <x:col min="3" max="3" width="24.1640625" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="28.08203125" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="33.25" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="47.9140625" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="7" width="43.1640625" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="53.6640625" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A1" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G2" s="5"/>
+      <x:c r="H2" s="1"/>
+    </x:row>
+    <x:row r="3" spans="1:8" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A3" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H3" s="1"/>
+    </x:row>
+    <x:row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A4" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D4" s="3"/>
+      <x:c r="E4" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H4" s="1"/>
+    </x:row>
+    <x:row r="5" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A5" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F5" s="1"/>
+      <x:c r="G5" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H5" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A6" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D6" s="3"/>
+      <x:c r="E6" s="3" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H6" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A7" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D7" s="3"/>
+      <x:c r="E7" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F7" s="1"/>
+      <x:c r="G7" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H7" s="1"/>
+    </x:row>
+    <x:row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A8" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F8" s="1"/>
+      <x:c r="G8" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H8" s="1"/>
+    </x:row>
+    <x:row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A9" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G9" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H9" s="1"/>
+    </x:row>
+    <x:row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A10" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D10" s="3"/>
+      <x:c r="E10" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F10" s="1"/>
+      <x:c r="G10" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H10" s="1"/>
+    </x:row>
+    <x:row r="11" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A11" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F11" s="1"/>
+      <x:c r="G11" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H11" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A12" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D12" s="3"/>
+      <x:c r="E12" s="3" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H12" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A13" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D13" s="3"/>
+      <x:c r="E13" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F13" s="1"/>
+      <x:c r="G13" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H13" s="1"/>
+    </x:row>
+    <x:row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A14" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D14" s="3"/>
+      <x:c r="E14" s="4" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F14" s="1"/>
+      <x:c r="G14" s="5">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H14" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A15" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D15" s="3"/>
+      <x:c r="E15" s="4" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F15" s="1"/>
+      <x:c r="G15" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H15" s="1" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A16" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D16" s="3"/>
+      <x:c r="E16" s="4" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F16" s="1"/>
+      <x:c r="G16" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H16" s="1"/>
+    </x:row>
+    <x:row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A17" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D17" s="3"/>
+      <x:c r="E17" s="4" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F17" s="1"/>
+      <x:c r="G17" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H17" s="1"/>
+    </x:row>
+    <x:row r="18" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A18" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D18" s="3"/>
+      <x:c r="E18" s="3" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F18" s="2" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H18" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A19" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D19" s="1"/>
+      <x:c r="E19" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F19" s="1"/>
+      <x:c r="G19" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H19" s="1"/>
+    </x:row>
+    <x:row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A20" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D20" s="1"/>
+      <x:c r="E20" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F20" s="1"/>
+      <x:c r="G20" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H20" s="1"/>
+    </x:row>
+    <x:row r="21" spans="1:8" ht="270" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A21" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D21" s="1"/>
+      <x:c r="E21" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F21" s="2" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H21" s="1"/>
+    </x:row>
+    <x:row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A22" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D22" s="1"/>
+      <x:c r="E22" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F22" s="1"/>
+      <x:c r="G22" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H22" s="1"/>
+    </x:row>
+    <x:row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A23" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D23" s="1"/>
+      <x:c r="E23" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F23" s="1"/>
+      <x:c r="G23" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H23" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A24" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H24" s="1"/>
+    </x:row>
+    <x:row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A25" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D25" s="1"/>
+      <x:c r="E25" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F25" s="1"/>
+      <x:c r="G25" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H25" s="1"/>
+    </x:row>
+    <x:row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A26" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D26" s="1"/>
+      <x:c r="E26" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F26" s="1"/>
+      <x:c r="G26" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H26" s="1"/>
+    </x:row>
+    <x:row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A27" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D27" s="1"/>
+      <x:c r="E27" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F27" s="1"/>
+      <x:c r="G27" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H27" s="1"/>
+    </x:row>
+    <x:row r="28" spans="1:8" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A28" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B28" s="2" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D28" s="1"/>
+      <x:c r="E28" s="1" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="F28" s="2" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G28" s="5" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H28" s="1" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A29" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D29" s="1"/>
+      <x:c r="E29" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F29" s="1"/>
+      <x:c r="G29" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H29" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A30" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D30" s="1"/>
+      <x:c r="E30" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F30" s="1"/>
+      <x:c r="G30" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H30" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E31" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F31" s="1"/>
+      <x:c r="G31" s="5">
+        <x:v>1207000000</x:v>
+      </x:c>
+      <x:c r="H31" s="5" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A32" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D32" s="1"/>
+      <x:c r="E32" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F32" s="1"/>
+      <x:c r="G32" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H32" s="1"/>
+    </x:row>
+    <x:row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A33" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D33" s="1"/>
+      <x:c r="E33" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F33" s="1"/>
+      <x:c r="G33" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H33" s="1"/>
+    </x:row>
+    <x:row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A34" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H34" s="1"/>
+    </x:row>
+    <x:row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A35" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D35" s="1"/>
+      <x:c r="E35" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F35" s="1"/>
+      <x:c r="G35" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H35" s="1"/>
+    </x:row>
+    <x:row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A36" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H36" s="1"/>
+    </x:row>
+    <x:row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A37" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D37" s="1"/>
+      <x:c r="E37" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F37" s="1"/>
+      <x:c r="G37" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H37" s="1"/>
+    </x:row>
+    <x:row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A38" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D38" s="1"/>
+      <x:c r="E38" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F38" s="1"/>
+      <x:c r="G38" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H38" s="1"/>
+    </x:row>
+    <x:row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A39" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D39" s="1"/>
+      <x:c r="E39" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G39" s="5">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H39" s="1"/>
+    </x:row>
+    <x:row r="40" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A40" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D40" s="1"/>
+      <x:c r="E40" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G40" s="5">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H40" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A41" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D41" s="1"/>
+      <x:c r="E41" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G41" s="5" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="H41" s="1"/>
+    </x:row>
+    <x:row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <x:c r="A42" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D42" s="1"/>
+      <x:c r="E42" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G42" s="5" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H42" s="1"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">（以下、新形式の JSON 要素：2026年10月追加。値を持つ JSON が1件でもある場合のみ列を出力。持たない JSON の出力は従来どおり）</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:nameIdentifier#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">著者識別子2(種別、URLとセット)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C44" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可(Scopus著者IDのみ想定)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D44" s="1"/>
+      <x:c r="E44" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F44" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.authors[*].identifiers.scopus</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G44" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">57000000001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H44" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">値を持つ著者位置のみ列を出力</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:nameIdentifier#2@nameIdentifierScheme</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">著者識別子2の種別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C45" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D45" s="1"/>
+      <x:c r="E45" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F45" s="1"/>
+      <x:c r="G45" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Scopus</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H45" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QIRで受け付ける値は要確認(設定ブロックの scopus_scheme)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:nameIdentifier#2@nameIdentifierURI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">著者識別子2のURL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C46" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" s="1"/>
+      <x:c r="E46" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル内の値から構築</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="1"/>
+      <x:c r="G46" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.scopus.com/authid/detail.uri?authorId=57000000001</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:familyName#1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">著者の姓(言語とセット)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" s="1"/>
+      <x:c r="E47" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.authors[*].family_name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tanaka</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H47" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">creatorName の後に出力。値を持つ著者位置のみ列を出力</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:familyName#1@xml:lang</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">著者の姓の言語</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" s="1"/>
+      <x:c r="E48" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="1"/>
+      <x:c r="G48" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">en</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:givenName#1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">著者の名(言語とセット)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C49" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" s="1"/>
+      <x:c r="E49" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.authors[*].given_name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G49" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Aiko</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H49" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1語の氏名では given_name が null のため出力しない(姓のみ)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:givenName#1@xml:lang</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">著者の名の言語</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C50" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D50" s="1"/>
+      <x:c r="E50" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F50" s="1"/>
+      <x:c r="G50" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">en</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:subject#4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主題分野(言語、種別とセット)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C51" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">可能(キーワードの後に続けて#4, #5…として展開)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D51" s="1"/>
+      <x:c r="E51" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F51" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.subjects[*]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G51" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Electronic, Optical and Magnetic Materials</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H51" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">番号はキーワードの続き(例はキーワード3件の場合)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:subject#4@xml:lang</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主題分野の言語</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C52" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D52" s="1"/>
+      <x:c r="E52" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" s="1"/>
+      <x:c r="G52" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">en</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:subject#4@subjectScheme</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B53" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主題分野の種別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" s="1"/>
+      <x:c r="E53" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="1"/>
+      <x:c r="G53" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Other</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H53" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">"Other" か "SciVal" かは要確認(設定ブロックの subject_area_scheme)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/datacite:date#2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">日付(受付日)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" s="1"/>
+      <x:c r="E54" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.manuscript_record.received</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G54" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-02-27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H54" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">manuscript_id を持つレコードのみ</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/datacite:date#2@dateType</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">日付の種別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C55" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D55" s="1"/>
+      <x:c r="E55" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F55" s="1"/>
+      <x:c r="G55" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Submitted</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/datacite:date#3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">日付(受理日)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" s="1"/>
+      <x:c r="E56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.manuscript_record.accepted</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G56" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-16</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">manuscript_id を持つレコードのみ(受付日が無い場合は#2)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/datacite:date#3@dateType</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">日付の種別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C57" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D57" s="1"/>
+      <x:c r="E57" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F57" s="1"/>
+      <x:c r="G57" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Accepted</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/dc:language#1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本文の言語</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" s="1"/>
+      <x:c r="E58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル(ISO 639-3に変換)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.language</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G58" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">eng</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">language が無い場合は設定ブロックの値(eng)。上の /dc:language#1 の行を置き換え</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">会議名(言語とセット)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C59" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" s="1"/>
+      <x:c r="E59" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F59" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.conference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G59" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QiR2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H59" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">略称。正式名称にするかは要確認。null(通常論文)は出力しない</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1@xml:lang</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">会議名の言語</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C60" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D60" s="1"/>
+      <x:c r="E60" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F60" s="1"/>
+      <x:c r="G60" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">en</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:autoFilter ref="A1:H42" xr:uid="{5A4BEA64-0C96-4527-8A58-FFDEC4514951}"/>
+  <x:phoneticPr fontId="1"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</x:worksheet>
 </file>
--- a/json2tsv/マッピング表.xlsx
+++ b/json2tsv/マッピング表.xlsx
@@ -1937,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{5A4BEA64-0C96-4527-8A58-FFDEC4514951}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:dimension ref="A1:H60"/>
+  <x:dimension ref="A1:H57"/>
   <x:sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <x:cols>
     <x:col min="1" max="1" width="66.6640625" bestFit="1" customWidth="1"/>
@@ -2864,17 +2864,17 @@
     <x:row r="44">
       <x:c r="A44" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:nameIdentifier#2</x:t>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:familyName#1</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">著者識別子2(種別、URLとセット)</x:t>
+          <x:t xml:space="preserve">著者の姓(言語とセット)</x:t>
         </x:is>
       </x:c>
       <x:c r="C44" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">不可(Scopus著者IDのみ想定)</x:t>
+          <x:t xml:space="preserve">不可</x:t>
         </x:is>
       </x:c>
       <x:c r="D44" s="1"/>
@@ -2885,29 +2885,29 @@
       </x:c>
       <x:c r="F44" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">$.authors[*].identifiers.scopus</x:t>
+          <x:t xml:space="preserve">$.authors[*].family_name</x:t>
         </x:is>
       </x:c>
       <x:c r="G44" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">57000000001</x:t>
+          <x:t xml:space="preserve">Tanaka</x:t>
         </x:is>
       </x:c>
       <x:c r="H44" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">値を持つ著者位置のみ列を出力</x:t>
+          <x:t xml:space="preserve">creatorName の後に出力。値を持つ著者位置のみ列を出力</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:nameIdentifier#2@nameIdentifierScheme</x:t>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:familyName#1@xml:lang</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">著者識別子2の種別</x:t>
+          <x:t xml:space="preserve">著者の姓の言語</x:t>
         </x:is>
       </x:c>
       <x:c r="C45" s="1" t="inlineStr">
@@ -2918,30 +2918,25 @@
       <x:c r="D45" s="1"/>
       <x:c r="E45" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
+          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="1"/>
       <x:c r="G45" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Scopus</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H45" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QIRで受け付ける値は要確認(設定ブロックの scopus_scheme)</x:t>
+          <x:t xml:space="preserve">en</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:nameIdentifier#2@nameIdentifierURI</x:t>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:givenName#1</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">著者識別子2のURL</x:t>
+          <x:t xml:space="preserve">著者の名(言語とセット)</x:t>
         </x:is>
       </x:c>
       <x:c r="C46" s="1" t="inlineStr">
@@ -2952,25 +2947,34 @@
       <x:c r="D46" s="1"/>
       <x:c r="E46" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JSONファイル内の値から構築</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F46" s="1"/>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.authors[*].given_name</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G46" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">https://www.scopus.com/authid/detail.uri?authorId=57000000001</x:t>
+          <x:t xml:space="preserve">Aiko</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H46" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1語の氏名では given_name が null のため出力しない(姓のみ)</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:familyName#1</x:t>
+          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:givenName#1@xml:lang</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">著者の姓(言語とセット)</x:t>
+          <x:t xml:space="preserve">著者の名の言語</x:t>
         </x:is>
       </x:c>
       <x:c r="C47" s="1" t="inlineStr">
@@ -2981,63 +2985,63 @@
       <x:c r="D47" s="1"/>
       <x:c r="E47" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JSONファイル</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F47" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$.authors[*].family_name</x:t>
-        </x:is>
-      </x:c>
+          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="1"/>
       <x:c r="G47" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tanaka</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H47" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">creatorName の後に出力。値を持つ著者位置のみ列を出力</x:t>
+          <x:t xml:space="preserve">en</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:familyName#1@xml:lang</x:t>
+          <x:t xml:space="preserve">/jpcoar:subject#4</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">著者の姓の言語</x:t>
+          <x:t xml:space="preserve">主題分野(言語、種別とセット)</x:t>
         </x:is>
       </x:c>
       <x:c r="C48" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">不可</x:t>
+          <x:t xml:space="preserve">可能(キーワードの後に続けて#4, #5…として展開)</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="1"/>
       <x:c r="E48" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F48" s="1"/>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.subjects[*]</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G48" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">en</x:t>
+          <x:t xml:space="preserve">Electronic, Optical and Magnetic Materials</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H48" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">番号はキーワードの続き(例はキーワード3件の場合)</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:givenName#1</x:t>
+          <x:t xml:space="preserve">/jpcoar:subject#4@xml:lang</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">著者の名(言語とセット)</x:t>
+          <x:t xml:space="preserve">主題分野の言語</x:t>
         </x:is>
       </x:c>
       <x:c r="C49" s="1" t="inlineStr">
@@ -3048,34 +3052,25 @@
       <x:c r="D49" s="1"/>
       <x:c r="E49" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JSONファイル</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F49" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$.authors[*].given_name</x:t>
-        </x:is>
-      </x:c>
+          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="1"/>
       <x:c r="G49" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Aiko</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H49" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1語の氏名では given_name が null のため出力しない(姓のみ)</x:t>
+          <x:t xml:space="preserve">en</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:creator#1/jpcoar:givenName#1@xml:lang</x:t>
+          <x:t xml:space="preserve">/jpcoar:subject#4@subjectScheme</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">著者の名の言語</x:t>
+          <x:t xml:space="preserve">主題分野の種別</x:t>
         </x:is>
       </x:c>
       <x:c r="C50" s="1" t="inlineStr">
@@ -3086,30 +3081,35 @@
       <x:c r="D50" s="1"/>
       <x:c r="E50" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
+          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="1"/>
       <x:c r="G50" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">en</x:t>
+          <x:t xml:space="preserve">Other</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H50" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分類コードではなく語のため Other(設定ブロックの subject_area_scheme)</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:subject#4</x:t>
+          <x:t xml:space="preserve">/datacite:date#2</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">主題分野(言語、種別とセット)</x:t>
+          <x:t xml:space="preserve">日付(受付日)</x:t>
         </x:is>
       </x:c>
       <x:c r="C51" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可能(キーワードの後に続けて#4, #5…として展開)</x:t>
+          <x:t xml:space="preserve">不可</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="1"/>
@@ -3120,29 +3120,29 @@
       </x:c>
       <x:c r="F51" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">$.subjects[*]</x:t>
+          <x:t xml:space="preserve">$.manuscript_record.received</x:t>
         </x:is>
       </x:c>
       <x:c r="G51" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Electronic, Optical and Magnetic Materials</x:t>
+          <x:t xml:space="preserve">2026-02-27</x:t>
         </x:is>
       </x:c>
       <x:c r="H51" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">番号はキーワードの続き(例はキーワード3件の場合)</x:t>
+          <x:t xml:space="preserve">manuscript_id を持つレコードのみ</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:subject#4@xml:lang</x:t>
+          <x:t xml:space="preserve">/datacite:date#2@dateType</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">主題分野の言語</x:t>
+          <x:t xml:space="preserve">日付の種別</x:t>
         </x:is>
       </x:c>
       <x:c r="C52" s="1" t="inlineStr">
@@ -3153,25 +3153,25 @@
       <x:c r="D52" s="1"/>
       <x:c r="E52" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
+          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="1"/>
       <x:c r="G52" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">en</x:t>
+          <x:t xml:space="preserve">Submitted</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:subject#4@subjectScheme</x:t>
+          <x:t xml:space="preserve">/datacite:date#3</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">主題分野の種別</x:t>
+          <x:t xml:space="preserve">日付(受理日)</x:t>
         </x:is>
       </x:c>
       <x:c r="C53" s="1" t="inlineStr">
@@ -3182,30 +3182,34 @@
       <x:c r="D53" s="1"/>
       <x:c r="E53" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F53" s="1"/>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.manuscript_record.accepted</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G53" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Other</x:t>
+          <x:t xml:space="preserve">2026-09-16</x:t>
         </x:is>
       </x:c>
       <x:c r="H53" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">"Other" か "SciVal" かは要確認(設定ブロックの subject_area_scheme)</x:t>
+          <x:t xml:space="preserve">manuscript_id を持つレコードのみ(受付日が無い場合は#2)</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/datacite:date#2</x:t>
+          <x:t xml:space="preserve">/datacite:date#3@dateType</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">日付(受付日)</x:t>
+          <x:t xml:space="preserve">日付の種別</x:t>
         </x:is>
       </x:c>
       <x:c r="C54" s="1" t="inlineStr">
@@ -3216,34 +3220,25 @@
       <x:c r="D54" s="1"/>
       <x:c r="E54" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JSONファイル</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F54" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$.manuscript_record.received</x:t>
-        </x:is>
-      </x:c>
+          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" s="1"/>
       <x:c r="G54" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2026-02-27</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H54" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">manuscript_id を持つレコードのみ</x:t>
+          <x:t xml:space="preserve">Accepted</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/datacite:date#2@dateType</x:t>
+          <x:t xml:space="preserve">/dc:language#1</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">日付の種別</x:t>
+          <x:t xml:space="preserve">本文の言語</x:t>
         </x:is>
       </x:c>
       <x:c r="C55" s="1" t="inlineStr">
@@ -3254,25 +3249,34 @@
       <x:c r="D55" s="1"/>
       <x:c r="E55" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F55" s="1"/>
+          <x:t xml:space="preserve">JSONファイル(ISO 639-3に変換)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F55" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.language</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G55" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Submitted</x:t>
+          <x:t xml:space="preserve">eng</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H55" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">language が無い場合は設定ブロックの値(eng)。上の /dc:language#1 の行を置き換え</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/datacite:date#3</x:t>
+          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">日付(受理日)</x:t>
+          <x:t xml:space="preserve">会議名(言語とセット)</x:t>
         </x:is>
       </x:c>
       <x:c r="C56" s="1" t="inlineStr">
@@ -3288,29 +3292,29 @@
       </x:c>
       <x:c r="F56" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">$.manuscript_record.accepted</x:t>
+          <x:t xml:space="preserve">$.conference</x:t>
         </x:is>
       </x:c>
       <x:c r="G56" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2026-09-16</x:t>
+          <x:t xml:space="preserve">QiR2025</x:t>
         </x:is>
       </x:c>
       <x:c r="H56" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">manuscript_id を持つレコードのみ(受付日が無い場合は#2)</x:t>
+          <x:t xml:space="preserve">特集号(会議)の略称。null(通常論文)は出力しない</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/datacite:date#3@dateType</x:t>
+          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1@xml:lang</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">日付の種別</x:t>
+          <x:t xml:space="preserve">会議名の言語</x:t>
         </x:is>
       </x:c>
       <x:c r="C57" s="1" t="inlineStr">
@@ -3321,116 +3325,11 @@
       <x:c r="D57" s="1"/>
       <x:c r="E57" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">コード内の設定ブロック</x:t>
+          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="1"/>
       <x:c r="G57" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Accepted</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">/dc:language#1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">本文の言語</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不可</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D58" s="1"/>
-      <x:c r="E58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">JSONファイル(ISO 639-3に変換)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$.language</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G58" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">eng</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">language が無い場合は設定ブロックの値(eng)。上の /dc:language#1 の行を置き換え</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B59" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">会議名(言語とセット)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C59" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不可</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D59" s="1"/>
-      <x:c r="E59" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">JSONファイル</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F59" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$.conference</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G59" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QiR2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H59" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">略称。正式名称にするかは要確認。null(通常論文)は出力しない</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1@xml:lang</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B60" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">会議名の言語</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C60" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不可</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D60" s="1"/>
-      <x:c r="E60" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F60" s="1"/>
-      <x:c r="G60" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">en</x:t>
         </x:is>

--- a/json2tsv/マッピング表.xlsx
+++ b/json2tsv/マッピング表.xlsx
@@ -1937,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{5A4BEA64-0C96-4527-8A58-FFDEC4514951}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:dimension ref="A1:H57"/>
+  <x:dimension ref="A1:H58"/>
   <x:sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <x:cols>
     <x:col min="1" max="1" width="66.6640625" bestFit="1" customWidth="1"/>
@@ -3271,12 +3271,12 @@
     <x:row r="56">
       <x:c r="A56" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1</x:t>
+          <x:t xml:space="preserve">/jpcoar:conference#1</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">会議名(言語とセット)</x:t>
+          <x:t xml:space="preserve">会議情報のヘッダ(会議名とセット)</x:t>
         </x:is>
       </x:c>
       <x:c r="C56" s="1" t="inlineStr">
@@ -3284,37 +3284,37 @@
           <x:t xml:space="preserve">不可</x:t>
         </x:is>
       </x:c>
-      <x:c r="D56" s="1"/>
+      <x:c r="D56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">会議名がある場合はヘッダとして必須(この列が無いとエラー)</x:t>
+        </x:is>
+      </x:c>
       <x:c r="E56" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">JSONファイル</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$.conference</x:t>
-        </x:is>
-      </x:c>
+          <x:t xml:space="preserve">取得不要</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" s="1"/>
       <x:c r="G56" s="5" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">QiR2025</x:t>
+          <x:t xml:space="preserve">値は出力しない(空セル)</x:t>
         </x:is>
       </x:c>
       <x:c r="H56" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">特集号(会議)の略称。null(通常論文)は出力しない</x:t>
+          <x:t xml:space="preserve">空列(値なし)</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1@xml:lang</x:t>
+          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">会議名の言語</x:t>
+          <x:t xml:space="preserve">会議名(言語とセット)</x:t>
         </x:is>
       </x:c>
       <x:c r="C57" s="1" t="inlineStr">
@@ -3325,11 +3325,49 @@
       <x:c r="D57" s="1"/>
       <x:c r="E57" s="1" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">JSONファイル</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F57" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">$.conference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G57" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QiR2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H57" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">特集号(会議)の略称。null(通常論文)は出力しない</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1@xml:lang</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">会議名の言語</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" s="1"/>
+      <x:c r="E58" s="1" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
         </x:is>
       </x:c>
-      <x:c r="F57" s="1"/>
-      <x:c r="G57" s="5" t="inlineStr">
+      <x:c r="F58" s="1"/>
+      <x:c r="G58" s="5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">en</x:t>
         </x:is>

--- a/json2tsv/マッピング表.xlsx
+++ b/json2tsv/マッピング表.xlsx
@@ -1937,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{5A4BEA64-0C96-4527-8A58-FFDEC4514951}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:dimension ref="A1:H58"/>
+  <x:dimension ref="A1:H55"/>
   <x:sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <x:cols>
     <x:col min="1" max="1" width="66.6640625" bestFit="1" customWidth="1"/>
@@ -3268,111 +3268,6 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">/jpcoar:conference#1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">会議情報のヘッダ(会議名とセット)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不可</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">会議名がある場合はヘッダとして必須(この列が無いとエラー)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">取得不要</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F56" s="1"/>
-      <x:c r="G56" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">値は出力しない(空セル)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">空列(値なし)</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B57" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">会議名(言語とセット)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C57" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不可</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D57" s="1"/>
-      <x:c r="E57" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">JSONファイル</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F57" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$.conference</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G57" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">QiR2025</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H57" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">特集号(会議)の略称。null(通常論文)は出力しない</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">/jpcoar:conference#1/jpcoar:conferenceName#1@xml:lang</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">会議名の言語</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不可</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D58" s="1"/>
-      <x:c r="E58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">JSONファイル内の値から判別</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F58" s="1"/>
-      <x:c r="G58" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">en</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:H42" xr:uid="{5A4BEA64-0C96-4527-8A58-FFDEC4514951}"/>
   <x:phoneticPr fontId="1"/>
